--- a/VerveStacks_PHL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_PHL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_PHL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8D71514-12C3-4B5D-8413-5E6A0A327552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFF7602F-4908-4B02-9192-559DA6D6115F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -934,265 +934,295 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_PHL_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_PHL_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_PHL_022</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 22</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_PHL_014</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_solelc_spv_PHL_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_PHL_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w1020283720-230_PHL</t>
+  </si>
+  <si>
+    <t>e_PH66-230_PHL,e_PH76-230_PHL</t>
+  </si>
+  <si>
+    <t>e_r15283858-230_PHL,e_w444278653-500_PHL</t>
+  </si>
+  <si>
+    <t>e_w444278653-500_PHL,e_PH58-500_PHL,e_w444226898-500_PHL,e_w936835406-500_PHL,e_PH60-230_PHL</t>
+  </si>
+  <si>
+    <t>e_w1064535276-230_PHL</t>
+  </si>
+  <si>
+    <t>e_w230069858-230_PHL,e_PH63-230_PHL,e_w168703936-230_PHL,e_PH65-230_PHL,e_PH62-230_PHL,e_w1421576367-230_PHL</t>
+  </si>
+  <si>
+    <t>e_PH15-230_PHL,e_w232660843-230_PHL,e_w727170005-230_PHL,e_w343559372-230_PHL</t>
+  </si>
+  <si>
+    <t>e_w249247868-230_PHL,e_PH4-230_PHL,e_w239879814-230_PHL,e_w727170005-230_PHL,e_w343559372-230_PHL</t>
+  </si>
+  <si>
+    <t>e_w1426217205-230_PHL,e_PH60-230_PHL,e_PH64-230_PHL,e_w168703936-230_PHL,e_PH66-230_PHL,e_w230069858-230_PHL</t>
+  </si>
+  <si>
+    <t>e_PH56-230_PHL,e_PH47-500_PHL,e_w168703936-230_PHL,e_w280280151-230_PHL</t>
+  </si>
+  <si>
+    <t>e_w449725900-230_PHL,e_w1268841071-230_PHL,e_PH80-230_PHL</t>
+  </si>
+  <si>
+    <t>e_w1426217205-230_PHL,e_w504311565-230_PHL,e_PH96-230_PHL,e_PH91-230_PHL,e_w246390064-230_PHL,e_w222760842-230_PHL,e_w222762510-230_PHL,e_w1268841071-230_PHL,e_PH77-230_PHL,e_PH76-230_PHL</t>
+  </si>
+  <si>
+    <t>e_w148697558-230_PHL,e_w449725900-230_PHL</t>
+  </si>
+  <si>
+    <t>e_w118685028-230_PHL,e_PH21-500_PHL,e_PH18-230_PHL,e_PH11-230_PHL,e_w1177962161-230_PHL,e_PH45-500_PHL,e_PH22-500_PHL,e_PH15-230_PHL</t>
+  </si>
+  <si>
+    <t>e_PH137-230_PHL,e_w487856247-230_PHL,e_w529099406-230_PHL</t>
+  </si>
+  <si>
+    <t>e_PH40-230_PHL,e_w232340888-230_PHL,e_PH19-230_PHL,e_w193890454-220_PHL,e_PH42-230_PHL,e_w1356506547-230_PHL,e_w528730876-230_PHL,e_PH5-230_PHL,e_PH3-230_PHL</t>
+  </si>
+  <si>
+    <t>e_PH1-230_PHL,e_w896657928-230_PHL,e_w1020283720-230_PHL</t>
+  </si>
+  <si>
+    <t>e_w1064535276-230_PHL,e_PH104-230_PHL,e_PH103-230_PHL,e_PH120-230_PHL,e_w242578663-230_PHL,e_w222762510-230_PHL,e_w449725900-230_PHL</t>
+  </si>
+  <si>
+    <t>e_w1268841071-230_PHL,e_PH80-230_PHL,e_PH76-230_PHL</t>
+  </si>
+  <si>
+    <t>e_PH53-500_PHL,e_w444278653-500_PHL,e_w449224249-230_PHL,e_w794493572-230_PHL,e_PH59-230_PHL,e_r8601923-230_PHL</t>
+  </si>
+  <si>
+    <t>e_w1426217205-230_PHL,e_w444278653-500_PHL,e_r15283858-230_PHL</t>
+  </si>
+  <si>
+    <t>e_r15283858-230_PHL,e_w1180784011-230_PHL,e_w1426217205-230_PHL</t>
+  </si>
+  <si>
+    <t>e_w487856247-230_PHL,e_w1064535276-230_PHL,e_w106994179-230_PHL,e_PH137-230_PHL</t>
+  </si>
+  <si>
     <t>e_w444278653-500_PHL,e_r15283858-230_PHL,e_w1426217205-230_PHL</t>
   </si>
   <si>
     <t>e_PH120-230_PHL,e_w106994179-230_PHL,e_w141727571-230_PHL,e_w449725900-230_PHL,e_w148697558-230_PHL</t>
   </si>
   <si>
-    <t>e_w249247868-230_PHL,e_PH4-230_PHL,e_w239879814-230_PHL,e_w727170005-230_PHL,e_w343559372-230_PHL</t>
-  </si>
-  <si>
-    <t>e_w1020283720-230_PHL</t>
-  </si>
-  <si>
-    <t>e_w1426217205-230_PHL,e_PH60-230_PHL,e_PH64-230_PHL,e_w168703936-230_PHL,e_PH66-230_PHL,e_w230069858-230_PHL</t>
-  </si>
-  <si>
-    <t>e_w1064535276-230_PHL</t>
-  </si>
-  <si>
-    <t>e_w230069858-230_PHL,e_PH63-230_PHL,e_w168703936-230_PHL,e_PH65-230_PHL,e_PH62-230_PHL,e_w1421576367-230_PHL</t>
-  </si>
-  <si>
-    <t>e_r15283858-230_PHL,e_w1180784011-230_PHL,e_w1426217205-230_PHL</t>
-  </si>
-  <si>
-    <t>e_w487856247-230_PHL,e_w1064535276-230_PHL,e_w106994179-230_PHL,e_PH137-230_PHL</t>
-  </si>
-  <si>
-    <t>e_r15283858-230_PHL,e_w444278653-500_PHL</t>
-  </si>
-  <si>
-    <t>e_w444278653-500_PHL,e_PH58-500_PHL,e_w444226898-500_PHL,e_w936835406-500_PHL,e_PH60-230_PHL</t>
-  </si>
-  <si>
-    <t>e_w118685028-230_PHL,e_PH21-500_PHL,e_PH18-230_PHL,e_PH11-230_PHL,e_w1177962161-230_PHL,e_PH45-500_PHL,e_PH22-500_PHL,e_PH15-230_PHL</t>
-  </si>
-  <si>
-    <t>e_PH137-230_PHL,e_w487856247-230_PHL,e_w529099406-230_PHL</t>
-  </si>
-  <si>
-    <t>e_PH15-230_PHL,e_w232660843-230_PHL,e_w727170005-230_PHL,e_w343559372-230_PHL</t>
-  </si>
-  <si>
-    <t>e_w148697558-230_PHL,e_w449725900-230_PHL</t>
-  </si>
-  <si>
-    <t>e_PH66-230_PHL,e_PH76-230_PHL</t>
-  </si>
-  <si>
-    <t>e_PH56-230_PHL,e_PH47-500_PHL,e_w168703936-230_PHL,e_w280280151-230_PHL</t>
-  </si>
-  <si>
-    <t>e_w449725900-230_PHL,e_w1268841071-230_PHL,e_PH80-230_PHL</t>
-  </si>
-  <si>
-    <t>e_w1426217205-230_PHL,e_w504311565-230_PHL,e_PH96-230_PHL,e_PH91-230_PHL,e_w246390064-230_PHL,e_w222760842-230_PHL,e_w222762510-230_PHL,e_w1268841071-230_PHL,e_PH77-230_PHL,e_PH76-230_PHL</t>
-  </si>
-  <si>
-    <t>e_PH40-230_PHL,e_w232340888-230_PHL,e_PH19-230_PHL,e_w193890454-220_PHL,e_PH42-230_PHL,e_w1356506547-230_PHL,e_w528730876-230_PHL,e_PH5-230_PHL,e_PH3-230_PHL</t>
-  </si>
-  <si>
-    <t>e_PH1-230_PHL,e_w896657928-230_PHL,e_w1020283720-230_PHL</t>
-  </si>
-  <si>
-    <t>e_w1064535276-230_PHL,e_PH104-230_PHL,e_PH103-230_PHL,e_PH120-230_PHL,e_w242578663-230_PHL,e_w222762510-230_PHL,e_w449725900-230_PHL</t>
-  </si>
-  <si>
-    <t>e_w1268841071-230_PHL,e_PH80-230_PHL,e_PH76-230_PHL</t>
-  </si>
-  <si>
-    <t>e_PH53-500_PHL,e_w444278653-500_PHL,e_w449224249-230_PHL,e_w794493572-230_PHL,e_PH59-230_PHL,e_r8601923-230_PHL</t>
-  </si>
-  <si>
-    <t>e_w1426217205-230_PHL,e_w444278653-500_PHL,e_r15283858-230_PHL</t>
+    <t>distr_wonelc_won_PHL_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_PHL_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_PHL_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_PHL_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_PHL_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wonelc_won_PHL_017</t>
@@ -1207,46 +1237,88 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
+    <t>distr_wonelc_won_PHL_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_PHL_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_PHL_010</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
+    <t>distr_wonelc_won_PHL_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_PHL_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_PHL_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_PHL_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_PHL_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_PHL_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_PHL_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_PHL_013</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wonelc_won_PHL_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_PHL_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_PHL_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_PHL_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_PHL_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
+    <t>distr_wonelc_won_PHL_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_PHL_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_PHL_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
   </si>
   <si>
     <t>distr_wonelc_won_PHL_008</t>
@@ -1261,82 +1333,40 @@
     <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wonelc_won_PHL_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_PHL_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_PHL_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_PHL_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_PHL_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_PHL_018</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wonelc_won_PHL_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_PHL_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_PHL_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_PHL_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_PHL_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_PHL_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_PHL_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
+    <t>elc_won_PHL_007</t>
+  </si>
+  <si>
+    <t>e_w444278653-500_PHL</t>
+  </si>
+  <si>
+    <t>elc_won_PHL_019</t>
+  </si>
+  <si>
+    <t>e_r15283858-230_PHL,e_w1426217205-230_PHL,e_w444278653-500_PHL,e_PH53-500_PHL,e_w449224249-230_PHL,e_w794493572-230_PHL,e_PH60-230_PHL,e_PH64-230_PHL</t>
+  </si>
+  <si>
+    <t>elc_won_PHL_015</t>
+  </si>
+  <si>
+    <t>e_PH42-230_PHL,e_w444278653-500_PHL,e_PH59-230_PHL,e_r8601923-230_PHL,e_w118685028-230_PHL,e_PH58-500_PHL,e_w1177962161-230_PHL,e_PH45-500_PHL,e_PH22-500_PHL</t>
+  </si>
+  <si>
+    <t>elc_won_PHL_016</t>
+  </si>
+  <si>
+    <t>e_w444226898-500_PHL,e_PH60-230_PHL,e_w168703936-230_PHL,e_w280280151-230_PHL,e_PH64-230_PHL,e_PH63-230_PHL</t>
+  </si>
+  <si>
+    <t>elc_won_PHL_003</t>
+  </si>
+  <si>
+    <t>e_w343559372-230_PHL,e_w1020283720-230_PHL</t>
   </si>
   <si>
     <t>elc_won_PHL_017</t>
@@ -1351,46 +1381,73 @@
     <t>e_w1064535276-230_PHL,e_PH120-230_PHL,e_w449725900-230_PHL</t>
   </si>
   <si>
+    <t>elc_won_PHL_020</t>
+  </si>
+  <si>
+    <t>elc_won_PHL_002</t>
+  </si>
+  <si>
+    <t>e_PH1-230_PHL,e_w896657928-230_PHL</t>
+  </si>
+  <si>
     <t>elc_won_PHL_010</t>
   </si>
   <si>
     <t>e_PH137-230_PHL</t>
   </si>
   <si>
+    <t>elc_won_PHL_011</t>
+  </si>
+  <si>
+    <t>e_PH104-230_PHL,e_PH103-230_PHL,e_w242578663-230_PHL</t>
+  </si>
+  <si>
+    <t>elc_won_PHL_014</t>
+  </si>
+  <si>
+    <t>e_w1268841071-230_PHL,e_PH80-230_PHL,e_w449725900-230_PHL</t>
+  </si>
+  <si>
+    <t>elc_won_PHL_005</t>
+  </si>
+  <si>
+    <t>elc_won_PHL_021</t>
+  </si>
+  <si>
+    <t>elc_won_PHL_004</t>
+  </si>
+  <si>
+    <t>e_PH15-230_PHL,e_w232660843-230_PHL,e_w343559372-230_PHL</t>
+  </si>
+  <si>
+    <t>elc_won_PHL_006</t>
+  </si>
+  <si>
+    <t>elc_won_PHL_023</t>
+  </si>
+  <si>
+    <t>e_r15283858-230_PHL,e_PH103-230_PHL,e_PH96-230_PHL,e_PH91-230_PHL,e_w222760842-230_PHL,e_w222762510-230_PHL</t>
+  </si>
+  <si>
     <t>elc_won_PHL_013</t>
   </si>
   <si>
     <t>e_w222762510-230_PHL,e_w1268841071-230_PHL,e_PH80-230_PHL</t>
   </si>
   <si>
-    <t>elc_won_PHL_007</t>
-  </si>
-  <si>
-    <t>e_w444278653-500_PHL</t>
-  </si>
-  <si>
-    <t>elc_won_PHL_019</t>
-  </si>
-  <si>
-    <t>e_r15283858-230_PHL,e_w1426217205-230_PHL,e_w444278653-500_PHL,e_PH53-500_PHL,e_w449224249-230_PHL,e_w794493572-230_PHL,e_PH60-230_PHL,e_PH64-230_PHL</t>
-  </si>
-  <si>
-    <t>elc_won_PHL_015</t>
-  </si>
-  <si>
-    <t>e_PH42-230_PHL,e_w444278653-500_PHL,e_PH59-230_PHL,e_r8601923-230_PHL,e_w118685028-230_PHL,e_PH58-500_PHL,e_w1177962161-230_PHL,e_PH45-500_PHL,e_PH22-500_PHL</t>
-  </si>
-  <si>
-    <t>elc_won_PHL_016</t>
-  </si>
-  <si>
-    <t>e_w444226898-500_PHL,e_PH60-230_PHL,e_w168703936-230_PHL,e_w280280151-230_PHL,e_PH64-230_PHL,e_PH63-230_PHL</t>
-  </si>
-  <si>
-    <t>elc_won_PHL_003</t>
-  </si>
-  <si>
-    <t>e_w343559372-230_PHL,e_w1020283720-230_PHL</t>
+    <t>elc_won_PHL_001</t>
+  </si>
+  <si>
+    <t>e_w896657928-230_PHL,e_w1020283720-230_PHL</t>
+  </si>
+  <si>
+    <t>elc_won_PHL_024</t>
+  </si>
+  <si>
+    <t>e_r15283858-230_PHL,e_w1426217205-230_PHL,e_w1180784011-230_PHL</t>
+  </si>
+  <si>
+    <t>elc_won_PHL_022</t>
   </si>
   <si>
     <t>elc_won_PHL_008</t>
@@ -1402,67 +1459,112 @@
     <t>elc_won_PHL_009</t>
   </si>
   <si>
-    <t>elc_won_PHL_024</t>
-  </si>
-  <si>
-    <t>e_r15283858-230_PHL,e_w1426217205-230_PHL,e_w1180784011-230_PHL</t>
-  </si>
-  <si>
-    <t>elc_won_PHL_022</t>
-  </si>
-  <si>
-    <t>elc_won_PHL_005</t>
-  </si>
-  <si>
-    <t>elc_won_PHL_021</t>
-  </si>
-  <si>
-    <t>elc_won_PHL_004</t>
-  </si>
-  <si>
-    <t>e_PH15-230_PHL,e_w232660843-230_PHL,e_w343559372-230_PHL</t>
-  </si>
-  <si>
     <t>elc_won_PHL_018</t>
   </si>
   <si>
     <t>e_w1426217205-230_PHL,e_w504311565-230_PHL,e_PH66-230_PHL,e_w230069858-230_PHL,e_w246390064-230_PHL,e_PH65-230_PHL,e_PH77-230_PHL,e_PH76-230_PHL,e_w1421576367-230_PHL</t>
   </si>
   <si>
-    <t>elc_won_PHL_020</t>
-  </si>
-  <si>
-    <t>elc_won_PHL_002</t>
-  </si>
-  <si>
-    <t>e_PH1-230_PHL,e_w896657928-230_PHL</t>
-  </si>
-  <si>
-    <t>elc_won_PHL_001</t>
-  </si>
-  <si>
-    <t>e_w896657928-230_PHL,e_w1020283720-230_PHL</t>
-  </si>
-  <si>
-    <t>elc_won_PHL_011</t>
-  </si>
-  <si>
-    <t>e_PH104-230_PHL,e_PH103-230_PHL,e_w242578663-230_PHL</t>
-  </si>
-  <si>
-    <t>elc_won_PHL_014</t>
-  </si>
-  <si>
-    <t>e_w1268841071-230_PHL,e_PH80-230_PHL,e_w449725900-230_PHL</t>
-  </si>
-  <si>
-    <t>elc_won_PHL_006</t>
-  </si>
-  <si>
-    <t>elc_won_PHL_023</t>
-  </si>
-  <si>
-    <t>e_r15283858-230_PHL,e_PH103-230_PHL,e_PH96-230_PHL,e_PH91-230_PHL,e_w222760842-230_PHL,e_w222762510-230_PHL</t>
+    <t>distr_wofelc_wof_PHL_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_PHL_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_PHL_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_PHL_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_PHL_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_PHL_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_PHL_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_PHL_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_PHL_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_PHL_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_PHL_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_PHL_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_PHL_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_PHL_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_PHL_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_PHL_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_PHL_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
   </si>
   <si>
     <t>distr_wofelc_wof_PHL_009</t>
@@ -1477,114 +1579,12 @@
     <t>connecting wind offshore to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_PHL_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_PHL_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_PHL_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_PHL_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_PHL_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_PHL_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_PHL_004</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_PHL_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_PHL_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_PHL_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_PHL_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_PHL_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_PHL_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_PHL_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_PHL_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_PHL_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_PHL_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_PHL_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_PHL_011</t>
   </si>
   <si>
@@ -1603,6 +1603,96 @@
     <t>connecting wind offshore to buses in cluster 12</t>
   </si>
   <si>
+    <t>elc_wof_PHL_005</t>
+  </si>
+  <si>
+    <t>e_PH53-500_PHL,e_PH40-230_PHL,e_w449224249-230_PHL</t>
+  </si>
+  <si>
+    <t>elc_wof_PHL_003</t>
+  </si>
+  <si>
+    <t>e_r15283858-230_PHL</t>
+  </si>
+  <si>
+    <t>elc_wof_PHL_013</t>
+  </si>
+  <si>
+    <t>e_w896657928-230_PHL</t>
+  </si>
+  <si>
+    <t>elc_wof_PHL_010</t>
+  </si>
+  <si>
+    <t>e_w193890454-220_PHL,e_w441960851-230_PHL,e_w896657928-230_PHL</t>
+  </si>
+  <si>
+    <t>elc_wof_PHL_019</t>
+  </si>
+  <si>
+    <t>e_PH80-230_PHL</t>
+  </si>
+  <si>
+    <t>elc_wof_PHL_021</t>
+  </si>
+  <si>
+    <t>e_w444278653-500_PHL,e_w1426217205-230_PHL</t>
+  </si>
+  <si>
+    <t>elc_wof_PHL_001</t>
+  </si>
+  <si>
+    <t>e_w449224249-230_PHL,e_w444278653-500_PHL</t>
+  </si>
+  <si>
+    <t>elc_wof_PHL_002</t>
+  </si>
+  <si>
+    <t>elc_wof_PHL_007</t>
+  </si>
+  <si>
+    <t>e_w449224249-230_PHL</t>
+  </si>
+  <si>
+    <t>elc_wof_PHL_017</t>
+  </si>
+  <si>
+    <t>e_w1426217205-230_PHL,e_w230069858-230_PHL,e_w504311565-230_PHL,e_PH66-230_PHL,e_w246390064-230_PHL,e_PH65-230_PHL,e_w1421576367-230_PHL</t>
+  </si>
+  <si>
+    <t>elc_wof_PHL_018</t>
+  </si>
+  <si>
+    <t>elc_wof_PHL_020</t>
+  </si>
+  <si>
+    <t>e_r15283858-230_PHL,e_w1426217205-230_PHL</t>
+  </si>
+  <si>
+    <t>elc_wof_PHL_008</t>
+  </si>
+  <si>
+    <t>elc_wof_PHL_015</t>
+  </si>
+  <si>
+    <t>e_PH56-230_PHL,e_PH45-500_PHL,e_PH15-230_PHL,e_w280280151-230_PHL,e_w232660843-230_PHL</t>
+  </si>
+  <si>
+    <t>elc_wof_PHL_016</t>
+  </si>
+  <si>
+    <t>e_w280280151-230_PHL,e_PH62-230_PHL,e_w447958186-230_PHL,e_w1421576367-230_PHL</t>
+  </si>
+  <si>
+    <t>elc_wof_PHL_006</t>
+  </si>
+  <si>
+    <t>elc_wof_PHL_023</t>
+  </si>
+  <si>
+    <t>e_PH60-230_PHL,e_PH64-230_PHL,e_w168703936-230_PHL</t>
+  </si>
+  <si>
     <t>elc_wof_PHL_009</t>
   </si>
   <si>
@@ -1612,100 +1702,10 @@
     <t>elc_wof_PHL_014</t>
   </si>
   <si>
-    <t>elc_wof_PHL_003</t>
-  </si>
-  <si>
-    <t>e_r15283858-230_PHL</t>
-  </si>
-  <si>
-    <t>elc_wof_PHL_006</t>
-  </si>
-  <si>
-    <t>e_w449224249-230_PHL,e_w444278653-500_PHL</t>
-  </si>
-  <si>
-    <t>elc_wof_PHL_023</t>
-  </si>
-  <si>
-    <t>e_PH60-230_PHL,e_PH64-230_PHL,e_w168703936-230_PHL</t>
-  </si>
-  <si>
-    <t>elc_wof_PHL_005</t>
-  </si>
-  <si>
-    <t>e_PH53-500_PHL,e_PH40-230_PHL,e_w449224249-230_PHL</t>
-  </si>
-  <si>
-    <t>elc_wof_PHL_010</t>
-  </si>
-  <si>
-    <t>e_w193890454-220_PHL,e_w441960851-230_PHL,e_w896657928-230_PHL</t>
-  </si>
-  <si>
-    <t>elc_wof_PHL_019</t>
-  </si>
-  <si>
-    <t>e_PH80-230_PHL</t>
-  </si>
-  <si>
     <t>elc_wof_PHL_004</t>
   </si>
   <si>
     <t>e_w449224249-230_PHL,e_PH53-500_PHL</t>
-  </si>
-  <si>
-    <t>elc_wof_PHL_021</t>
-  </si>
-  <si>
-    <t>e_w444278653-500_PHL,e_w1426217205-230_PHL</t>
-  </si>
-  <si>
-    <t>elc_wof_PHL_001</t>
-  </si>
-  <si>
-    <t>elc_wof_PHL_002</t>
-  </si>
-  <si>
-    <t>elc_wof_PHL_007</t>
-  </si>
-  <si>
-    <t>e_w449224249-230_PHL</t>
-  </si>
-  <si>
-    <t>elc_wof_PHL_017</t>
-  </si>
-  <si>
-    <t>e_w1426217205-230_PHL,e_w230069858-230_PHL,e_w504311565-230_PHL,e_PH66-230_PHL,e_w246390064-230_PHL,e_PH65-230_PHL,e_w1421576367-230_PHL</t>
-  </si>
-  <si>
-    <t>elc_wof_PHL_018</t>
-  </si>
-  <si>
-    <t>elc_wof_PHL_013</t>
-  </si>
-  <si>
-    <t>e_w896657928-230_PHL</t>
-  </si>
-  <si>
-    <t>elc_wof_PHL_020</t>
-  </si>
-  <si>
-    <t>e_r15283858-230_PHL,e_w1426217205-230_PHL</t>
-  </si>
-  <si>
-    <t>elc_wof_PHL_008</t>
-  </si>
-  <si>
-    <t>elc_wof_PHL_015</t>
-  </si>
-  <si>
-    <t>e_PH56-230_PHL,e_PH45-500_PHL,e_PH15-230_PHL,e_w280280151-230_PHL,e_w232660843-230_PHL</t>
-  </si>
-  <si>
-    <t>elc_wof_PHL_016</t>
-  </si>
-  <si>
-    <t>e_w280280151-230_PHL,e_PH62-230_PHL,e_w447958186-230_PHL,e_w1421576367-230_PHL</t>
   </si>
   <si>
     <t>elc_wof_PHL_011</t>
@@ -7328,7 +7328,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E927774A-2F3B-497D-8676-0E3C99449888}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF8F2CBB-4AE3-44D4-96CD-E1A44A0D66DC}">
   <dimension ref="B9:BD39"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7566,16 +7566,16 @@
         <v>268</v>
       </c>
       <c r="Y11" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="Z11" t="s">
         <v>330</v>
       </c>
       <c r="AA11">
-        <v>0.98091331037183915</v>
+        <v>0.98339439155331498</v>
       </c>
       <c r="AB11">
-        <v>349.92264318294986</v>
+        <v>304.43615485589299</v>
       </c>
       <c r="AD11" t="s">
         <v>267</v>
@@ -7608,10 +7608,10 @@
         <v>404</v>
       </c>
       <c r="AO11">
-        <v>0.99770980913553242</v>
+        <v>0.98456671064014578</v>
       </c>
       <c r="AP11">
-        <v>41.986832515239605</v>
+        <v>282.9436382639949</v>
       </c>
       <c r="AR11" t="s">
         <v>267</v>
@@ -7644,10 +7644,10 @@
         <v>492</v>
       </c>
       <c r="BC11">
-        <v>0.97461449766377517</v>
+        <v>0.9694753599195608</v>
       </c>
       <c r="BD11">
-        <v>465.40087616412279</v>
+        <v>559.61840147471878</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7712,16 +7712,16 @@
         <v>272</v>
       </c>
       <c r="Y12" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="Z12" t="s">
         <v>331</v>
       </c>
       <c r="AA12">
-        <v>0.99765912383256905</v>
+        <v>0.99396589777723887</v>
       </c>
       <c r="AB12">
-        <v>42.916063069567031</v>
+        <v>110.62520741728831</v>
       </c>
       <c r="AD12" t="s">
         <v>267</v>
@@ -7754,10 +7754,10 @@
         <v>406</v>
       </c>
       <c r="AO12">
-        <v>0.99406280383936318</v>
+        <v>0.99248985985111937</v>
       </c>
       <c r="AP12">
-        <v>108.84859627834065</v>
+        <v>137.68590272947768</v>
       </c>
       <c r="AR12" t="s">
         <v>267</v>
@@ -7787,13 +7787,13 @@
         <v>493</v>
       </c>
       <c r="BB12" t="s">
-        <v>437</v>
+        <v>494</v>
       </c>
       <c r="BC12">
-        <v>0.99382081155816415</v>
+        <v>0.95247189331844051</v>
       </c>
       <c r="BD12">
-        <v>113.28512143365793</v>
+        <v>871.34862249525702</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7858,16 +7858,16 @@
         <v>274</v>
       </c>
       <c r="Y13" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="Z13" t="s">
         <v>332</v>
       </c>
       <c r="AA13">
-        <v>0.99791656052513211</v>
+        <v>0.96534857645154915</v>
       </c>
       <c r="AB13">
-        <v>38.196390372578811</v>
+        <v>635.27609838826606</v>
       </c>
       <c r="AD13" t="s">
         <v>267</v>
@@ -7900,10 +7900,10 @@
         <v>408</v>
       </c>
       <c r="AO13">
-        <v>0.99608005694626323</v>
+        <v>0.99907083612455716</v>
       </c>
       <c r="AP13">
-        <v>71.865622651841079</v>
+        <v>17.034671049785612</v>
       </c>
       <c r="AR13" t="s">
         <v>267</v>
@@ -7930,16 +7930,16 @@
         <v>449</v>
       </c>
       <c r="BA13" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="BB13" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="BC13">
-        <v>0.95247189331844051</v>
+        <v>0.99736092250007091</v>
       </c>
       <c r="BD13">
-        <v>871.34862249525702</v>
+        <v>48.383087498700846</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8004,16 +8004,16 @@
         <v>276</v>
       </c>
       <c r="Y14" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="Z14" t="s">
         <v>333</v>
       </c>
       <c r="AA14">
-        <v>0.99823681798928865</v>
+        <v>0.99818188636243754</v>
       </c>
       <c r="AB14">
-        <v>32.325003529707992</v>
+        <v>33.332083355312307</v>
       </c>
       <c r="AD14" t="s">
         <v>267</v>
@@ -8046,10 +8046,10 @@
         <v>410</v>
       </c>
       <c r="AO14">
-        <v>0.99573253918947924</v>
+        <v>0.99786098379740285</v>
       </c>
       <c r="AP14">
-        <v>78.236781526213051</v>
+        <v>39.215297047614307</v>
       </c>
       <c r="AR14" t="s">
         <v>267</v>
@@ -8076,16 +8076,16 @@
         <v>451</v>
       </c>
       <c r="BA14" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="BB14" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="BC14">
-        <v>0.9649620207290458</v>
+        <v>0.9952468939944521</v>
       </c>
       <c r="BD14">
-        <v>642.36295330082771</v>
+        <v>87.140276768377845</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8150,16 +8150,16 @@
         <v>278</v>
       </c>
       <c r="Y15" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="Z15" t="s">
         <v>334</v>
       </c>
       <c r="AA15">
-        <v>0.99575911694982822</v>
+        <v>0.99376777269044003</v>
       </c>
       <c r="AB15">
-        <v>77.749522586482627</v>
+        <v>114.25750067526708</v>
       </c>
       <c r="AD15" t="s">
         <v>267</v>
@@ -8192,10 +8192,10 @@
         <v>412</v>
       </c>
       <c r="AO15">
-        <v>0.98456671064014578</v>
+        <v>0.99597109918381066</v>
       </c>
       <c r="AP15">
-        <v>282.9436382639949</v>
+        <v>73.863181630138158</v>
       </c>
       <c r="AR15" t="s">
         <v>267</v>
@@ -8222,16 +8222,16 @@
         <v>453</v>
       </c>
       <c r="BA15" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="BB15" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="BC15">
-        <v>0.99256830222305958</v>
+        <v>0.99014178201499103</v>
       </c>
       <c r="BD15">
-        <v>136.24779257724143</v>
+        <v>180.73399639183009</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8299,7 +8299,7 @@
         <v>245</v>
       </c>
       <c r="Z16" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AA16">
         <v>0.97160199730371832</v>
@@ -8338,10 +8338,10 @@
         <v>414</v>
       </c>
       <c r="AO16">
-        <v>0.99248985985111937</v>
+        <v>0.99770980913553242</v>
       </c>
       <c r="AP16">
-        <v>137.68590272947768</v>
+        <v>41.986832515239605</v>
       </c>
       <c r="AR16" t="s">
         <v>267</v>
@@ -8368,16 +8368,16 @@
         <v>455</v>
       </c>
       <c r="BA16" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="BB16" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="BC16">
-        <v>0.9694753599195608</v>
+        <v>0.98701837308846752</v>
       </c>
       <c r="BD16">
-        <v>559.61840147471878</v>
+        <v>237.99649337809595</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8445,7 +8445,7 @@
         <v>264</v>
       </c>
       <c r="Z17" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AA17">
         <v>0.99846207823216582</v>
@@ -8484,10 +8484,10 @@
         <v>416</v>
       </c>
       <c r="AO17">
-        <v>0.99907083612455716</v>
+        <v>0.99406280383936318</v>
       </c>
       <c r="AP17">
-        <v>17.034671049785612</v>
+        <v>108.84859627834065</v>
       </c>
       <c r="AR17" t="s">
         <v>267</v>
@@ -8514,16 +8514,16 @@
         <v>457</v>
       </c>
       <c r="BA17" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="BB17" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="BC17">
-        <v>0.9952468939944521</v>
+        <v>0.94726561864078151</v>
       </c>
       <c r="BD17">
-        <v>87.140276768377845</v>
+        <v>966.79699158567212</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8588,16 +8588,16 @@
         <v>284</v>
       </c>
       <c r="Y18" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="Z18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AA18">
-        <v>0.99630694356078808</v>
+        <v>0.99780224722054478</v>
       </c>
       <c r="AB18">
-        <v>67.706034718884723</v>
+        <v>40.292134290012825</v>
       </c>
       <c r="AD18" t="s">
         <v>267</v>
@@ -8627,13 +8627,13 @@
         <v>417</v>
       </c>
       <c r="AN18" t="s">
-        <v>418</v>
+        <v>334</v>
       </c>
       <c r="AO18">
-        <v>0.99786098379740285</v>
+        <v>0.96497764359814764</v>
       </c>
       <c r="AP18">
-        <v>39.215297047614307</v>
+        <v>642.07653403395977</v>
       </c>
       <c r="AR18" t="s">
         <v>267</v>
@@ -8660,16 +8660,16 @@
         <v>459</v>
       </c>
       <c r="BA18" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="BB18" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="BC18">
-        <v>0.99014178201499103</v>
+        <v>0.96108117452289532</v>
       </c>
       <c r="BD18">
-        <v>180.73399639183009</v>
+        <v>713.5118004135868</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8734,16 +8734,16 @@
         <v>286</v>
       </c>
       <c r="Y19" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Z19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AA19">
-        <v>0.99570061448016733</v>
+        <v>0.99791656052513211</v>
       </c>
       <c r="AB19">
-        <v>78.822067863598875</v>
+        <v>38.196390372578811</v>
       </c>
       <c r="AD19" t="s">
         <v>267</v>
@@ -8770,16 +8770,16 @@
         <v>371</v>
       </c>
       <c r="AM19" t="s">
+        <v>418</v>
+      </c>
+      <c r="AN19" t="s">
         <v>419</v>
       </c>
-      <c r="AN19" t="s">
-        <v>420</v>
-      </c>
       <c r="AO19">
-        <v>0.99597109918381066</v>
+        <v>0.9981398026279793</v>
       </c>
       <c r="AP19">
-        <v>73.863181630138158</v>
+        <v>34.103618487045566</v>
       </c>
       <c r="AR19" t="s">
         <v>267</v>
@@ -8812,10 +8812,10 @@
         <v>507</v>
       </c>
       <c r="BC19">
-        <v>0.95222475524835148</v>
+        <v>0.98218260337789753</v>
       </c>
       <c r="BD19">
-        <v>875.87948711355568</v>
+        <v>326.65227140521222</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8880,16 +8880,16 @@
         <v>288</v>
       </c>
       <c r="Y20" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Z20" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="AA20">
-        <v>0.96534857645154915</v>
+        <v>0.99823681798928865</v>
       </c>
       <c r="AB20">
-        <v>635.27609838826606</v>
+        <v>32.325003529707992</v>
       </c>
       <c r="AD20" t="s">
         <v>267</v>
@@ -8916,16 +8916,16 @@
         <v>373</v>
       </c>
       <c r="AM20" t="s">
+        <v>420</v>
+      </c>
+      <c r="AN20" t="s">
         <v>421</v>
       </c>
-      <c r="AN20" t="s">
-        <v>422</v>
-      </c>
       <c r="AO20">
-        <v>0.99852911903912533</v>
+        <v>0.99608005694626323</v>
       </c>
       <c r="AP20">
-        <v>26.966150949369744</v>
+        <v>71.865622651841079</v>
       </c>
       <c r="AR20" t="s">
         <v>267</v>
@@ -8958,10 +8958,10 @@
         <v>509</v>
       </c>
       <c r="BC20">
-        <v>0.98701837308846752</v>
+        <v>0.9954518231085866</v>
       </c>
       <c r="BD20">
-        <v>237.99649337809595</v>
+        <v>83.383243009245319</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9026,16 +9026,16 @@
         <v>290</v>
       </c>
       <c r="Y21" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Z21" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AA21">
-        <v>0.99818188636243754</v>
+        <v>0.99575911694982822</v>
       </c>
       <c r="AB21">
-        <v>33.332083355312307</v>
+        <v>77.749522586482627</v>
       </c>
       <c r="AD21" t="s">
         <v>267</v>
@@ -9062,16 +9062,16 @@
         <v>375</v>
       </c>
       <c r="AM21" t="s">
+        <v>422</v>
+      </c>
+      <c r="AN21" t="s">
         <v>423</v>
       </c>
-      <c r="AN21" t="s">
-        <v>408</v>
-      </c>
       <c r="AO21">
-        <v>0.99482472296381985</v>
+        <v>0.99628427617720494</v>
       </c>
       <c r="AP21">
-        <v>94.880078996636385</v>
+        <v>68.121603417908631</v>
       </c>
       <c r="AR21" t="s">
         <v>267</v>
@@ -9101,13 +9101,13 @@
         <v>510</v>
       </c>
       <c r="BB21" t="s">
-        <v>497</v>
+        <v>421</v>
       </c>
       <c r="BC21">
-        <v>0.94726561864078151</v>
+        <v>0.99324871992207653</v>
       </c>
       <c r="BD21">
-        <v>966.79699158567212</v>
+        <v>123.77346809526369</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9172,16 +9172,16 @@
         <v>292</v>
       </c>
       <c r="Y22" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="Z22" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="AA22">
-        <v>0.99376777269044003</v>
+        <v>0.99777112657155465</v>
       </c>
       <c r="AB22">
-        <v>114.25750067526708</v>
+        <v>40.862679521498755</v>
       </c>
       <c r="AD22" t="s">
         <v>267</v>
@@ -9214,10 +9214,10 @@
         <v>425</v>
       </c>
       <c r="AO22">
-        <v>0.9956809332001243</v>
+        <v>0.99251912420603017</v>
       </c>
       <c r="AP22">
-        <v>79.182891331054464</v>
+        <v>137.14938955611294</v>
       </c>
       <c r="AR22" t="s">
         <v>267</v>
@@ -9247,13 +9247,13 @@
         <v>511</v>
       </c>
       <c r="BB22" t="s">
-        <v>495</v>
+        <v>512</v>
       </c>
       <c r="BC22">
-        <v>0.96108117452289532</v>
+        <v>0.98334996736073688</v>
       </c>
       <c r="BD22">
-        <v>713.5118004135868</v>
+        <v>305.25059838649065</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9318,16 +9318,16 @@
         <v>294</v>
       </c>
       <c r="Y23" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="Z23" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AA23">
-        <v>0.99952167827010774</v>
+        <v>0.99040701874142978</v>
       </c>
       <c r="AB23">
-        <v>8.7692317146905214</v>
+        <v>175.8713230737871</v>
       </c>
       <c r="AD23" t="s">
         <v>267</v>
@@ -9357,13 +9357,13 @@
         <v>426</v>
       </c>
       <c r="AN23" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="AO23">
-        <v>0.97839868790765439</v>
+        <v>0.96226341174990382</v>
       </c>
       <c r="AP23">
-        <v>396.02405502633599</v>
+        <v>691.83745125176267</v>
       </c>
       <c r="AR23" t="s">
         <v>267</v>
@@ -9390,16 +9390,16 @@
         <v>469</v>
       </c>
       <c r="BA23" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="BB23" t="s">
-        <v>513</v>
+        <v>404</v>
       </c>
       <c r="BC23">
-        <v>0.98218260337789753</v>
+        <v>0.98270500068433009</v>
       </c>
       <c r="BD23">
-        <v>326.65227140521222</v>
+        <v>317.07498745394764</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9464,16 +9464,16 @@
         <v>296</v>
       </c>
       <c r="Y24" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="Z24" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AA24">
-        <v>0.99816370589456072</v>
+        <v>0.99831152163399195</v>
       </c>
       <c r="AB24">
-        <v>33.665391933052938</v>
+        <v>30.955436710147502</v>
       </c>
       <c r="AD24" t="s">
         <v>267</v>
@@ -9503,13 +9503,13 @@
         <v>427</v>
       </c>
       <c r="AN24" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="AO24">
-        <v>0.96226341174990382</v>
+        <v>0.9905595837772998</v>
       </c>
       <c r="AP24">
-        <v>691.83745125176267</v>
+        <v>173.07429741616966</v>
       </c>
       <c r="AR24" t="s">
         <v>267</v>
@@ -9542,10 +9542,10 @@
         <v>515</v>
       </c>
       <c r="BC24">
-        <v>0.9954518231085866</v>
+        <v>0.99657169671114076</v>
       </c>
       <c r="BD24">
-        <v>83.383243009245319</v>
+        <v>62.852226962418733</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9610,16 +9610,16 @@
         <v>298</v>
       </c>
       <c r="Y25" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="Z25" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AA25">
-        <v>0.99780224722054478</v>
+        <v>0.9941320730310681</v>
       </c>
       <c r="AB25">
-        <v>40.292134290012825</v>
+        <v>107.57866109708571</v>
       </c>
       <c r="AD25" t="s">
         <v>267</v>
@@ -9649,13 +9649,13 @@
         <v>428</v>
       </c>
       <c r="AN25" t="s">
-        <v>335</v>
+        <v>429</v>
       </c>
       <c r="AO25">
-        <v>0.9905595837772998</v>
+        <v>0.99534232229151143</v>
       </c>
       <c r="AP25">
-        <v>173.07429741616966</v>
+        <v>85.390757988957404</v>
       </c>
       <c r="AR25" t="s">
         <v>267</v>
@@ -9685,13 +9685,13 @@
         <v>516</v>
       </c>
       <c r="BB25" t="s">
-        <v>408</v>
+        <v>517</v>
       </c>
       <c r="BC25">
-        <v>0.99324871992207653</v>
+        <v>0.99449729807118203</v>
       </c>
       <c r="BD25">
-        <v>123.77346809526369</v>
+        <v>100.88286869499547</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9756,16 +9756,16 @@
         <v>300</v>
       </c>
       <c r="Y26" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="Z26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AA26">
-        <v>0.9941320730310681</v>
+        <v>0.99952167827010774</v>
       </c>
       <c r="AB26">
-        <v>107.57866109708571</v>
+        <v>8.7692317146905214</v>
       </c>
       <c r="AD26" t="s">
         <v>267</v>
@@ -9792,16 +9792,16 @@
         <v>385</v>
       </c>
       <c r="AM26" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN26" t="s">
-        <v>430</v>
+        <v>332</v>
       </c>
       <c r="AO26">
-        <v>0.99534232229151143</v>
+        <v>0.97592815785972808</v>
       </c>
       <c r="AP26">
-        <v>85.390757988957404</v>
+        <v>441.31710590498483</v>
       </c>
       <c r="AR26" t="s">
         <v>267</v>
@@ -9828,16 +9828,16 @@
         <v>475</v>
       </c>
       <c r="BA26" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="BB26" t="s">
-        <v>518</v>
+        <v>504</v>
       </c>
       <c r="BC26">
-        <v>0.99736092250007091</v>
+        <v>0.9649620207290458</v>
       </c>
       <c r="BD26">
-        <v>48.383087498700846</v>
+        <v>642.36295330082771</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9902,16 +9902,16 @@
         <v>302</v>
       </c>
       <c r="Y27" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="Z27" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AA27">
-        <v>0.99396589777723887</v>
+        <v>0.99816370589456072</v>
       </c>
       <c r="AB27">
-        <v>110.62520741728831</v>
+        <v>33.665391933052938</v>
       </c>
       <c r="AD27" t="s">
         <v>267</v>
@@ -9944,10 +9944,10 @@
         <v>432</v>
       </c>
       <c r="AO27">
-        <v>0.9962299619396654</v>
+        <v>0.9988153294944212</v>
       </c>
       <c r="AP27">
-        <v>69.117364439467778</v>
+        <v>21.718959268944548</v>
       </c>
       <c r="AR27" t="s">
         <v>267</v>
@@ -9980,10 +9980,10 @@
         <v>520</v>
       </c>
       <c r="BC27">
-        <v>0.98334996736073688</v>
+        <v>0.99256830222305958</v>
       </c>
       <c r="BD27">
-        <v>305.25059838649065</v>
+        <v>136.24779257724143</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10048,16 +10048,16 @@
         <v>304</v>
       </c>
       <c r="Y28" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="Z28" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="AA28">
-        <v>0.98339439155331498</v>
+        <v>0.99888694922270271</v>
       </c>
       <c r="AB28">
-        <v>304.43615485589299</v>
+        <v>20.405930917117111</v>
       </c>
       <c r="AD28" t="s">
         <v>267</v>
@@ -10087,13 +10087,13 @@
         <v>433</v>
       </c>
       <c r="AN28" t="s">
-        <v>335</v>
+        <v>434</v>
       </c>
       <c r="AO28">
-        <v>0.96497764359814764</v>
+        <v>0.99573253918947924</v>
       </c>
       <c r="AP28">
-        <v>642.07653403395977</v>
+        <v>78.236781526213051</v>
       </c>
       <c r="AR28" t="s">
         <v>267</v>
@@ -10123,13 +10123,13 @@
         <v>521</v>
       </c>
       <c r="BB28" t="s">
-        <v>412</v>
+        <v>522</v>
       </c>
       <c r="BC28">
-        <v>0.98270500068433009</v>
+        <v>0.97461449766377517</v>
       </c>
       <c r="BD28">
-        <v>317.07498745394764</v>
+        <v>465.40087616412279</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10194,16 +10194,16 @@
         <v>306</v>
       </c>
       <c r="Y29" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="Z29" t="s">
         <v>346</v>
       </c>
       <c r="AA29">
-        <v>0.99777112657155465</v>
+        <v>0.99759019746600464</v>
       </c>
       <c r="AB29">
-        <v>40.862679521498755</v>
+        <v>44.179713123248369</v>
       </c>
       <c r="AD29" t="s">
         <v>267</v>
@@ -10230,16 +10230,16 @@
         <v>391</v>
       </c>
       <c r="AM29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO29">
-        <v>0.9981398026279793</v>
+        <v>0.99564221922003138</v>
       </c>
       <c r="AP29">
-        <v>34.103618487045566</v>
+        <v>79.892647632758653</v>
       </c>
       <c r="AR29" t="s">
         <v>267</v>
@@ -10266,16 +10266,16 @@
         <v>481</v>
       </c>
       <c r="BA29" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="BB29" t="s">
-        <v>523</v>
+        <v>436</v>
       </c>
       <c r="BC29">
-        <v>0.99657169671114076</v>
+        <v>0.99382081155816415</v>
       </c>
       <c r="BD29">
-        <v>62.852226962418733</v>
+        <v>113.28512143365793</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10340,16 +10340,16 @@
         <v>308</v>
       </c>
       <c r="Y30" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="Z30" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="AA30">
-        <v>0.99040701874142978</v>
+        <v>0.98324893337605057</v>
       </c>
       <c r="AB30">
-        <v>175.8713230737871</v>
+        <v>307.10288810573968</v>
       </c>
       <c r="AD30" t="s">
         <v>267</v>
@@ -10376,16 +10376,16 @@
         <v>393</v>
       </c>
       <c r="AM30" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN30" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO30">
-        <v>0.99564221922003138</v>
+        <v>0.9956809332001243</v>
       </c>
       <c r="AP30">
-        <v>79.892647632758653</v>
+        <v>79.182891331054464</v>
       </c>
       <c r="AR30" t="s">
         <v>267</v>
@@ -10418,10 +10418,10 @@
         <v>525</v>
       </c>
       <c r="BC30">
-        <v>0.99449729807118203</v>
+        <v>0.95222475524835148</v>
       </c>
       <c r="BD30">
-        <v>100.88286869499547</v>
+        <v>875.87948711355568</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10486,16 +10486,16 @@
         <v>310</v>
       </c>
       <c r="Y31" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="Z31" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA31">
-        <v>0.99831152163399195</v>
+        <v>0.99652907241247102</v>
       </c>
       <c r="AB31">
-        <v>30.955436710147502</v>
+        <v>63.633672438030523</v>
       </c>
       <c r="AD31" t="s">
         <v>267</v>
@@ -10522,16 +10522,16 @@
         <v>395</v>
       </c>
       <c r="AM31" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN31" t="s">
-        <v>439</v>
+        <v>334</v>
       </c>
       <c r="AO31">
-        <v>0.99628427617720494</v>
+        <v>0.97839868790765439</v>
       </c>
       <c r="AP31">
-        <v>68.121603417908631</v>
+        <v>396.02405502633599</v>
       </c>
       <c r="AR31" t="s">
         <v>267</v>
@@ -10632,16 +10632,16 @@
         <v>312</v>
       </c>
       <c r="Y32" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="Z32" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AA32">
-        <v>0.99888694922270271</v>
+        <v>0.99606221692548491</v>
       </c>
       <c r="AB32">
-        <v>20.405930917117111</v>
+        <v>72.192689699443079</v>
       </c>
       <c r="AD32" t="s">
         <v>267</v>
@@ -10674,10 +10674,10 @@
         <v>441</v>
       </c>
       <c r="AO32">
-        <v>0.99251912420603017</v>
+        <v>0.99852911903912533</v>
       </c>
       <c r="AP32">
-        <v>137.14938955611294</v>
+        <v>26.966150949369744</v>
       </c>
       <c r="AR32" t="s">
         <v>267</v>
@@ -10778,16 +10778,16 @@
         <v>314</v>
       </c>
       <c r="Y33" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="Z33" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="AA33">
-        <v>0.99759019746600464</v>
+        <v>0.95999823382043226</v>
       </c>
       <c r="AB33">
-        <v>44.179713123248369</v>
+        <v>733.36571329207618</v>
       </c>
       <c r="AD33" t="s">
         <v>267</v>
@@ -10817,13 +10817,13 @@
         <v>442</v>
       </c>
       <c r="AN33" t="s">
-        <v>339</v>
+        <v>421</v>
       </c>
       <c r="AO33">
-        <v>0.97592815785972808</v>
+        <v>0.99482472296381985</v>
       </c>
       <c r="AP33">
-        <v>441.31710590498483</v>
+        <v>94.880078996636385</v>
       </c>
       <c r="AR33" t="s">
         <v>267</v>
@@ -10853,7 +10853,7 @@
         <v>530</v>
       </c>
       <c r="BB33" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="BC33">
         <v>0.98223913695768794</v>
@@ -10924,16 +10924,16 @@
         <v>316</v>
       </c>
       <c r="Y34" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="Z34" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="AA34">
-        <v>0.98324893337605057</v>
+        <v>0.99855411957743645</v>
       </c>
       <c r="AB34">
-        <v>307.10288810573968</v>
+        <v>26.507807746998349</v>
       </c>
       <c r="AD34" t="s">
         <v>267</v>
@@ -10966,10 +10966,10 @@
         <v>444</v>
       </c>
       <c r="AO34">
-        <v>0.9988153294944212</v>
+        <v>0.9962299619396654</v>
       </c>
       <c r="AP34">
-        <v>21.718959268944548</v>
+        <v>69.117364439467778</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11034,16 +11034,16 @@
         <v>318</v>
       </c>
       <c r="Y35" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="Z35" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AA35">
-        <v>0.99652907241247102</v>
+        <v>0.9919581965545663</v>
       </c>
       <c r="AB35">
-        <v>63.633672438030523</v>
+        <v>147.43306316628397</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11108,16 +11108,16 @@
         <v>320</v>
       </c>
       <c r="Y36" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Z36" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AA36">
-        <v>0.99606221692548491</v>
+        <v>0.99630694356078808</v>
       </c>
       <c r="AB36">
-        <v>72.192689699443079</v>
+        <v>67.706034718884723</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11182,16 +11182,16 @@
         <v>322</v>
       </c>
       <c r="Y37" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Z37" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="AA37">
-        <v>0.95999823382043226</v>
+        <v>0.99570061448016733</v>
       </c>
       <c r="AB37">
-        <v>733.36571329207618</v>
+        <v>78.822067863598875</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11256,16 +11256,16 @@
         <v>324</v>
       </c>
       <c r="Y38" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Z38" t="s">
         <v>353</v>
       </c>
       <c r="AA38">
-        <v>0.99855411957743645</v>
+        <v>0.98091331037183915</v>
       </c>
       <c r="AB38">
-        <v>26.507807746998349</v>
+        <v>349.92264318294986</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11330,16 +11330,16 @@
         <v>326</v>
       </c>
       <c r="Y39" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="Z39" t="s">
         <v>354</v>
       </c>
       <c r="AA39">
-        <v>0.9919581965545663</v>
+        <v>0.99765912383256905</v>
       </c>
       <c r="AB39">
-        <v>147.43306316628397</v>
+        <v>42.916063069567031</v>
       </c>
     </row>
   </sheetData>
@@ -11348,7 +11348,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6589D042-C552-4F99-A7F0-EE032FC1D7F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F60707-0E5E-4186-87C1-0A18DA71CAE4}">
   <dimension ref="B9:Z34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11460,7 +11460,7 @@
         <v>531</v>
       </c>
       <c r="K11" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="L11">
         <v>6.5845233157164564</v>
@@ -11493,7 +11493,7 @@
         <v>579</v>
       </c>
       <c r="X11" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="Y11">
         <v>10.53375</v>
@@ -11528,7 +11528,7 @@
         <v>533</v>
       </c>
       <c r="K12" t="s">
-        <v>434</v>
+        <v>418</v>
       </c>
       <c r="L12">
         <v>3.6684590822916472</v>
@@ -11561,7 +11561,7 @@
         <v>581</v>
       </c>
       <c r="X12" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="Y12">
         <v>8.3797499999999996</v>
@@ -11596,7 +11596,7 @@
         <v>535</v>
       </c>
       <c r="K13" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="L13">
         <v>2.4620480159063574</v>
@@ -11629,7 +11629,7 @@
         <v>583</v>
       </c>
       <c r="X13" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="Y13">
         <v>10.204499999999999</v>
@@ -11664,7 +11664,7 @@
         <v>537</v>
       </c>
       <c r="K14" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L14">
         <v>4.0732201684820639</v>
@@ -11697,7 +11697,7 @@
         <v>585</v>
       </c>
       <c r="X14" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
       <c r="Y14">
         <v>11.49225</v>
@@ -11732,7 +11732,7 @@
         <v>539</v>
       </c>
       <c r="K15" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L15">
         <v>1.6248524872184931</v>
@@ -11765,7 +11765,7 @@
         <v>587</v>
       </c>
       <c r="X15" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="Y15">
         <v>13.15875</v>
@@ -11800,7 +11800,7 @@
         <v>541</v>
       </c>
       <c r="K16" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="L16">
         <v>5.2357383243485023</v>
@@ -11833,7 +11833,7 @@
         <v>589</v>
       </c>
       <c r="X16" t="s">
-        <v>496</v>
+        <v>518</v>
       </c>
       <c r="Y16">
         <v>25.39875</v>
@@ -11868,7 +11868,7 @@
         <v>543</v>
       </c>
       <c r="K17" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="L17">
         <v>3.0779501857340072</v>
@@ -11901,7 +11901,7 @@
         <v>591</v>
       </c>
       <c r="X17" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="Y17">
         <v>1.9844999999999999</v>
@@ -11936,7 +11936,7 @@
         <v>545</v>
       </c>
       <c r="K18" t="s">
-        <v>421</v>
+        <v>440</v>
       </c>
       <c r="L18">
         <v>1.9424523895521892</v>
@@ -11969,7 +11969,7 @@
         <v>593</v>
       </c>
       <c r="X18" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="Y18">
         <v>8.0129999999999999</v>
@@ -12004,7 +12004,7 @@
         <v>547</v>
       </c>
       <c r="K19" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="L19">
         <v>0.77922250202460941</v>
@@ -12037,7 +12037,7 @@
         <v>595</v>
       </c>
       <c r="X19" t="s">
-        <v>491</v>
+        <v>521</v>
       </c>
       <c r="Y19">
         <v>24.00675</v>
@@ -12072,7 +12072,7 @@
         <v>549</v>
       </c>
       <c r="K20" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="L20">
         <v>0.38552403516737821</v>
@@ -12105,7 +12105,7 @@
         <v>597</v>
       </c>
       <c r="X20" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="Y20">
         <v>2.6114999999999999</v>
@@ -12140,7 +12140,7 @@
         <v>551</v>
       </c>
       <c r="K21" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="L21">
         <v>8.5458794740569086</v>
@@ -12208,7 +12208,7 @@
         <v>553</v>
       </c>
       <c r="K22" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="L22">
         <v>1.6374936511471578</v>
@@ -12276,7 +12276,7 @@
         <v>555</v>
       </c>
       <c r="K23" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="L23">
         <v>3.3248681026086038</v>
@@ -12309,7 +12309,7 @@
         <v>603</v>
       </c>
       <c r="X23" t="s">
-        <v>517</v>
+        <v>495</v>
       </c>
       <c r="Y23">
         <v>3.8294999999999999</v>
@@ -12344,7 +12344,7 @@
         <v>557</v>
       </c>
       <c r="K24" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="L24">
         <v>4.65991188661617</v>
@@ -12377,7 +12377,7 @@
         <v>605</v>
       </c>
       <c r="X24" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="Y24">
         <v>24.972750000000001</v>
@@ -12412,7 +12412,7 @@
         <v>559</v>
       </c>
       <c r="K25" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="L25">
         <v>20.983484907215406</v>
@@ -12445,7 +12445,7 @@
         <v>607</v>
       </c>
       <c r="X25" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="Y25">
         <v>13.889250000000001</v>
@@ -12480,7 +12480,7 @@
         <v>561</v>
       </c>
       <c r="K26" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="L26">
         <v>11.10598066571092</v>
@@ -12513,7 +12513,7 @@
         <v>609</v>
       </c>
       <c r="X26" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="Y26">
         <v>32.036999999999999</v>
@@ -12548,7 +12548,7 @@
         <v>563</v>
       </c>
       <c r="K27" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="L27">
         <v>12.71792252204758</v>
@@ -12581,7 +12581,7 @@
         <v>611</v>
       </c>
       <c r="X27" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="Y27">
         <v>37.801499999999997</v>
@@ -12616,7 +12616,7 @@
         <v>565</v>
       </c>
       <c r="K28" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="L28">
         <v>25.976177149847992</v>
@@ -12649,7 +12649,7 @@
         <v>613</v>
       </c>
       <c r="X28" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="Y28">
         <v>2.5057499999999999</v>
@@ -12684,7 +12684,7 @@
         <v>567</v>
       </c>
       <c r="K29" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="L29">
         <v>10.344494934739773</v>
@@ -12717,7 +12717,7 @@
         <v>615</v>
       </c>
       <c r="X29" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="Y29">
         <v>5.5012499999999998</v>
@@ -12752,7 +12752,7 @@
         <v>569</v>
       </c>
       <c r="K30" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="L30">
         <v>7.3374667928236123E-3</v>
@@ -12785,7 +12785,7 @@
         <v>617</v>
       </c>
       <c r="X30" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="Y30">
         <v>29.286000000000001</v>
@@ -12820,7 +12820,7 @@
         <v>571</v>
       </c>
       <c r="K31" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L31">
         <v>0.8051710306174682</v>
@@ -12853,7 +12853,7 @@
         <v>619</v>
       </c>
       <c r="X31" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="Y31">
         <v>55.189500000000002</v>
@@ -12888,7 +12888,7 @@
         <v>573</v>
       </c>
       <c r="K32" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="L32">
         <v>1.3706449368975455E-3</v>
@@ -12956,7 +12956,7 @@
         <v>575</v>
       </c>
       <c r="K33" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="L33">
         <v>8.9106405161177875</v>
@@ -12989,7 +12989,7 @@
         <v>623</v>
       </c>
       <c r="X33" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
       <c r="Y33">
         <v>8.7855000000000008</v>
@@ -13024,7 +13024,7 @@
         <v>577</v>
       </c>
       <c r="K34" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="L34">
         <v>14.480848161918972</v>
@@ -13039,7 +13039,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A300DC5-4037-4D07-B1D3-FF3672DA03C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{197361D3-8750-4490-893F-D9A76F9192E6}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14856,7 +14856,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA486990-46A7-4C38-9D87-6DF9A5D3E5B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0531ED4E-4995-46F9-AF42-275ADB41A6A6}">
   <dimension ref="B2:M61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -15033,7 +15033,7 @@
         <v>656</v>
       </c>
       <c r="C8" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D8" t="s">
         <v>657</v>
@@ -15068,7 +15068,7 @@
         <v>657</v>
       </c>
       <c r="D9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -15161,7 +15161,7 @@
         <v>663</v>
       </c>
       <c r="C12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D12" t="s">
         <v>664</v>
@@ -15196,7 +15196,7 @@
         <v>664</v>
       </c>
       <c r="D13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E13">
         <v>1</v>
